--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
@@ -1016,7 +1016,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{771e7361-0c05-4042-84cc-47393818fae6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783b9355-8313-4177-b39e-0ded7f002ade}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
@@ -1016,7 +1016,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{783b9355-8313-4177-b39e-0ded7f002ade}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34f9e3aa-fd02-4208-9e3a-bb3fb68a8163}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Pie Chart_report.xlsx
@@ -1016,7 +1016,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34f9e3aa-fd02-4208-9e3a-bb3fb68a8163}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{b2383d03-9294-4e20-b3aa-91b31cd2359f}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
